--- a/content/smart-health/docs/diccionario_datos.xlsx
+++ b/content/smart-health/docs/diccionario_datos.xlsx
@@ -13,20 +13,26 @@
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="12" r:id="rId1"/>
-    <sheet name="CLIENTS" sheetId="1" r:id="rId2"/>
-    <sheet name="DOCTORS" sheetId="2" r:id="rId3"/>
-    <sheet name="APPOINTMENTS" sheetId="3" r:id="rId4"/>
-    <sheet name="MEDICAL_RECORDS" sheetId="4" r:id="rId5"/>
-    <sheet name="PRESCRIPTIONS" sheetId="5" r:id="rId6"/>
-    <sheet name="MEDICATIONS" sheetId="6" r:id="rId7"/>
-    <sheet name="SPECIALTIES" sheetId="7" r:id="rId8"/>
-    <sheet name="DIAGNOSES" sheetId="8" r:id="rId9"/>
-    <sheet name="DOCUMENT_TYPES" sheetId="9" r:id="rId10"/>
-    <sheet name="LANGUAGES" sheetId="13" r:id="rId11"/>
-    <sheet name="ADRESSES" sheetId="14" r:id="rId12"/>
-    <sheet name="ROOMS" sheetId="15" r:id="rId13"/>
-    <sheet name="DEPARTMENTS" sheetId="16" r:id="rId14"/>
-    <sheet name="MUNICIPALITIES" sheetId="17" r:id="rId15"/>
+    <sheet name="PATIENTS" sheetId="1" r:id="rId2"/>
+    <sheet name="PATIENT_PHONES" sheetId="18" r:id="rId3"/>
+    <sheet name="PATIENT_ADDRESSES" sheetId="19" r:id="rId4"/>
+    <sheet name="PATIENT_ALLERGIES" sheetId="20" r:id="rId5"/>
+    <sheet name="DOCTOR_ADDRESSES" sheetId="21" r:id="rId6"/>
+    <sheet name="DOCTOR_SPECIALTIES" sheetId="22" r:id="rId7"/>
+    <sheet name="RECORD_DIAGNOSES" sheetId="23" r:id="rId8"/>
+    <sheet name="DOCTORS" sheetId="2" r:id="rId9"/>
+    <sheet name="APPOINTMENTS" sheetId="3" r:id="rId10"/>
+    <sheet name="MEDICAL_RECORDS" sheetId="4" r:id="rId11"/>
+    <sheet name="PRESCRIPTIONS" sheetId="5" r:id="rId12"/>
+    <sheet name="MEDICATIONS" sheetId="6" r:id="rId13"/>
+    <sheet name="SPECIALTIES" sheetId="7" r:id="rId14"/>
+    <sheet name="DIAGNOSES" sheetId="8" r:id="rId15"/>
+    <sheet name="DOCUMENT_TYPES" sheetId="9" r:id="rId16"/>
+    <sheet name="LANGUAGES" sheetId="13" r:id="rId17"/>
+    <sheet name="ADRESSES" sheetId="14" r:id="rId18"/>
+    <sheet name="ROOMS" sheetId="15" r:id="rId19"/>
+    <sheet name="DEPARTMENTS" sheetId="16" r:id="rId20"/>
+    <sheet name="MUNICIPALITIES" sheetId="17" r:id="rId21"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -44,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="305">
   <si>
     <t>Campo</t>
   </si>
@@ -70,9 +76,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>Propósito</t>
   </si>
   <si>
@@ -88,9 +91,6 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
     <t>Catalogo de Datos - Informacion General</t>
   </si>
   <si>
@@ -166,12 +166,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>TIMESTAMP</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
     <t>DEFAULT FALSE</t>
   </si>
   <si>
-    <t>Ciudad donde se encuentra el comercio</t>
-  </si>
-  <si>
     <t>Jhon Jairo Mantilla Castellanos</t>
   </si>
   <si>
@@ -346,9 +337,6 @@
     <t xml:space="preserve"> Correo electrónico</t>
   </si>
   <si>
-    <t>Género del paciente</t>
-  </si>
-  <si>
     <t>Fecha de nacimiento</t>
   </si>
   <si>
@@ -424,18 +412,12 @@
     <t>creation_date</t>
   </si>
   <si>
-    <t>chk_appointment_time</t>
-  </si>
-  <si>
     <t>TIME</t>
   </si>
   <si>
     <t>TEXT</t>
   </si>
   <si>
-    <t>CHECK</t>
-  </si>
-  <si>
     <t>Identificador único de la cita</t>
   </si>
   <si>
@@ -445,9 +427,6 @@
     <t>Referencia al médico</t>
   </si>
   <si>
-    <t>Sala</t>
-  </si>
-  <si>
     <t>Fecha de la cita</t>
   </si>
   <si>
@@ -469,9 +448,6 @@
     <t>Fecha de creación</t>
   </si>
   <si>
-    <t>Valida tiempo inicio &lt; fin</t>
-  </si>
-  <si>
     <t>medical_record_id</t>
   </si>
   <si>
@@ -571,9 +547,6 @@
     <t>active_ingredient</t>
   </si>
   <si>
-    <t>Principio activo</t>
-  </si>
-  <si>
     <t>presentation</t>
   </si>
   <si>
@@ -727,9 +700,6 @@
     <t xml:space="preserve"> Ubicación física</t>
   </si>
   <si>
-    <t>CLIENTS</t>
-  </si>
-  <si>
     <t>department_code</t>
   </si>
   <si>
@@ -748,9 +718,6 @@
     <t>Código único del departamento</t>
   </si>
   <si>
-    <t>municipality_id</t>
-  </si>
-  <si>
     <t>municipality_name</t>
   </si>
   <si>
@@ -758,6 +725,342 @@
   </si>
   <si>
     <t>DEPARTMENTS</t>
+  </si>
+  <si>
+    <t>PATIENT_PHONES</t>
+  </si>
+  <si>
+    <t>PATIENT_ADDRESSES</t>
+  </si>
+  <si>
+    <t>PATIENT_ALLERGIES</t>
+  </si>
+  <si>
+    <t>DOCTOR_SPECIALTIES</t>
+  </si>
+  <si>
+    <t>DOCTOR_ADDRESSES</t>
+  </si>
+  <si>
+    <t>RECORD_DIAGNOSES</t>
+  </si>
+  <si>
+    <t>Almacena los números telefónicos de los pacientes, incluyendo el tipo de teléfono y si es el principal</t>
+  </si>
+  <si>
+    <t>Concatenan los datos de dirección comunes a los históricos del paciente asociados con estas direcciones</t>
+  </si>
+  <si>
+    <t>Contienen información sobre las alergias de los pacientes y la gravedad del efecto</t>
+  </si>
+  <si>
+    <t>Registra las direcciones asociadas a los doctores con tipos de dirección y horarios de oficina</t>
+  </si>
+  <si>
+    <t>Tabla intermedia N:M entre médicos y especialidades</t>
+  </si>
+  <si>
+    <t>Asocia diagnósticos a registros clínicos</t>
+  </si>
+  <si>
+    <t>CHAR</t>
+  </si>
+  <si>
+    <t>CHECK(gender IN('M','F','O'))</t>
+  </si>
+  <si>
+    <t>Género del paciente(masculiono, femenino,otro)</t>
+  </si>
+  <si>
+    <t>patient_phone_id</t>
+  </si>
+  <si>
+    <t>Identificador único del teléfono</t>
+  </si>
+  <si>
+    <t>phone_type</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOT NULL, CHECK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (phone_type IN ('Móvil','Fijo'))</t>
+    </r>
+  </si>
+  <si>
+    <t>Número de teléfono</t>
+  </si>
+  <si>
+    <t>is_primary</t>
+  </si>
+  <si>
+    <t>Indica si es el teléfono principal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+  </si>
+  <si>
+    <t>teléfono--&gt; (Mobile: Móvil, Landline: Fijo)</t>
+  </si>
+  <si>
+    <t>patient_address_id</t>
+  </si>
+  <si>
+    <t>Identificador único de la relación</t>
+  </si>
+  <si>
+    <t>Referencia a la dirección</t>
+  </si>
+  <si>
+    <t>address_type</t>
+  </si>
+  <si>
+    <t>Indica si es la dirección principal</t>
+  </si>
+  <si>
+    <t>valid_from</t>
+  </si>
+  <si>
+    <t>Fecha de inicio de validez</t>
+  </si>
+  <si>
+    <t>valid_to</t>
+  </si>
+  <si>
+    <t>Fecha de fin de validez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de dirección </t>
+  </si>
+  <si>
+    <t>Referencia con paciente</t>
+  </si>
+  <si>
+    <t>Referencia condirección</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>patient_allergy_id</t>
+  </si>
+  <si>
+    <t>Identificador único de la alergia</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>reaction_description</t>
+  </si>
+  <si>
+    <t>Descripción de la reacción alérgica</t>
+  </si>
+  <si>
+    <t>diagnosed_date</t>
+  </si>
+  <si>
+    <t>nivel de alergia (Mild: Leve, Moderate: Moderada, Severe: Severa)</t>
+  </si>
+  <si>
+    <t>Fecha de diagnóstico</t>
+  </si>
+  <si>
+    <t>medicamento referenciado</t>
+  </si>
+  <si>
+    <t>paciente referenciado</t>
+  </si>
+  <si>
+    <t>NOT NULL, UNIQUE</t>
+  </si>
+  <si>
+    <t>doctor_specialty_id</t>
+  </si>
+  <si>
+    <t>certification_date</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>Restricción</t>
+  </si>
+  <si>
+    <t>Fecha de certificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Médico referenciado</t>
+  </si>
+  <si>
+    <t>especialidad referenciada</t>
+  </si>
+  <si>
+    <t>especialidad activa</t>
+  </si>
+  <si>
+    <t>doctor_address_id</t>
+  </si>
+  <si>
+    <t>office_hours</t>
+  </si>
+  <si>
+    <t>Horario de atención</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tipo de direccion (Office: Consultorio, Hospital: Hospital)</t>
+  </si>
+  <si>
+    <t>es lugar principal de práctica o no</t>
+  </si>
+  <si>
+    <t>Código único del municipio</t>
+  </si>
+  <si>
+    <t>Nombre completo del municipio</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SERIAL</t>
+  </si>
+  <si>
+    <t>NOT NULL,UNIQUE</t>
+  </si>
+  <si>
+    <t>nombre comercial de medicamento</t>
+  </si>
+  <si>
+    <t>ingreduebte activo del medicamento</t>
+  </si>
+  <si>
+    <t>NOT NULL,CHECK</t>
+  </si>
+  <si>
+    <t>Sala referenciada</t>
+  </si>
+  <si>
+    <t>médico referenciado</t>
+  </si>
+  <si>
+    <t>record_diagnosis_id</t>
+  </si>
+  <si>
+    <t>Referencia al registro médico</t>
+  </si>
+  <si>
+    <t>Referencia al diagnóstico</t>
+  </si>
+  <si>
+    <t>diagnosis_type</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOT NULL, CHECK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (diagnosis_type IN ('Principal','Secondary','Differential'))</t>
+    </r>
+  </si>
+  <si>
+    <t>Tipo de diagnóstico (Principal, Secundario, Diferencial)</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Notas adicionales sobre el diagnóstico</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>FK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>1.2</t>
   </si>
 </sst>
 </file>
@@ -847,7 +1150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,8 +1199,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -920,12 +1229,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1018,6 +1364,69 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1048,8 +1457,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1452,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
@@ -1460,447 +1867,556 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="A1" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="A2" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:8" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
     </row>
     <row r="4" spans="1:8" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+        <v>8</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="51">
+        <v>9</v>
+      </c>
+      <c r="B5" s="74">
         <v>45960</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
+        <v>10</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="51">
-        <v>45960</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
+        <v>11</v>
+      </c>
+      <c r="B7" s="74">
+        <v>45970</v>
+      </c>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+    </row>
+    <row r="9" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A9" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-    </row>
-    <row r="9" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A9" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
     </row>
     <row r="10" spans="1:8" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
+        <v>15</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
     </row>
     <row r="11" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+        <v>16</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
     </row>
     <row r="12" spans="1:8" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
+        <v>17</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
     </row>
     <row r="13" spans="1:8" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:8" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+        <v>28</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
+        <v>29</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+    </row>
+    <row r="17" spans="1:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-    </row>
-    <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-    </row>
-    <row r="18" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+    </row>
+    <row r="19" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+    </row>
+    <row r="20" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+    </row>
+    <row r="21" spans="1:15" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B21" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+    </row>
+    <row r="22" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="43" t="s">
+      <c r="B22" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+    </row>
+    <row r="23" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+    </row>
+    <row r="24" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+    </row>
+    <row r="25" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+    </row>
+    <row r="26" spans="1:15" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+    </row>
+    <row r="27" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+    </row>
+    <row r="28" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+    </row>
+    <row r="29" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+    </row>
+    <row r="30" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+    </row>
+    <row r="31" spans="1:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
+        <v>225</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+    </row>
+    <row r="32" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="G32" s="63"/>
+      <c r="H32" s="64"/>
+      <c r="O32" s="42"/>
+    </row>
+    <row r="33" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-    </row>
-    <row r="19" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-    </row>
-    <row r="20" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-    </row>
-    <row r="21" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-    </row>
-    <row r="22" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-    </row>
-    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-    </row>
-    <row r="24" spans="1:8" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-    </row>
-    <row r="25" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-    </row>
-    <row r="26" spans="1:8" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-    </row>
-    <row r="27" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-    </row>
-    <row r="28" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-    </row>
-    <row r="29" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="44" t="s">
-        <v>224</v>
-      </c>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-    </row>
-    <row r="30" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-    </row>
+      <c r="B33" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="60"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="62" t="s">
+        <v>227</v>
+      </c>
+      <c r="G33" s="63"/>
+      <c r="H33" s="64"/>
+    </row>
+    <row r="34" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="62" t="s">
+        <v>229</v>
+      </c>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+    </row>
+    <row r="35" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="63"/>
+      <c r="H35" s="64"/>
+    </row>
+    <row r="36" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="G36" s="63"/>
+      <c r="H36" s="64"/>
+    </row>
+    <row r="37" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="44"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+    </row>
+    <row r="38" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="58">
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B15:H15"/>
@@ -1945,9 +2461,22 @@
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F36:H36"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F18:H18" location="CLIENTS!A1" display="CLIENTS!A1"/>
     <hyperlink ref="F19:H19" location="DOCTORS!A1" display="DOCTORS!A1"/>
     <hyperlink ref="F20:H20" location="APPOINTMENTS!A1" display="APPOINTMENTS!A1"/>
     <hyperlink ref="F21:H21" location="MEDICAL_RECORDS!A1" display="MEDICAL_RECORDS!A1"/>
@@ -1960,6 +2489,13 @@
     <hyperlink ref="F30:H30" location="ROOMS!A1" display="ROOMS!A1"/>
     <hyperlink ref="F28:H28" location="MUNICIPALITIES!A1" display="MUNICIPALITIES!A1"/>
     <hyperlink ref="F27:H27" location="DEPARTMENTS!A1" display="DEPARTMENTS!A1"/>
+    <hyperlink ref="F31:H31" location="PATIENT_PHONES!A1" display="PATIENT_PHONES!A1"/>
+    <hyperlink ref="F32:H32" location="PATIENT_ADDRESSES!A1" display="PATIENT_ADDRESSES!A1"/>
+    <hyperlink ref="F33:H33" location="PATIENT_ALLERGIES!A1" display="PATIENT_ALLERGIES!A1"/>
+    <hyperlink ref="F34:H34" location="DOCTOR_ADDRESSES!A1" display="DOCTOR_ADDRESSES!A1"/>
+    <hyperlink ref="F35:H35" location="DOCTOR_SPECIALTIES!A1" display="DOCTOR_SPECIALTIES!A1"/>
+    <hyperlink ref="F36:H36" location="RECORD_DIAGNOSES!A1" display="RECORD_DIAGNOSES!A1"/>
+    <hyperlink ref="F18:H18" location="PATIENTS!A1" display="PATIENTS!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -1972,1206 +2508,141 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>70</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="21">
-        <v>10</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>10</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="21">
-        <v>100</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="21">
-        <v>100</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>222</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>10</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="21">
-        <v>255</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="21">
-        <v>20</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>205</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>50</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="21">
-        <v>50</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="21">
-        <v>100</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="41" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="38.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C2" s="8">
-        <v>10</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="53"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="52"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="5" max="5" width="39.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C2" s="8">
-        <v>10</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9">
-        <v>100</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="29">
-        <v>10</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="16">
-        <v>50</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="17">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="18">
-        <v>50</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="18">
-        <v>50</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="16">
-        <v>10</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="17">
-        <v>255</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="20">
-        <v>50</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="31.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="12">
-        <v>20</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="12">
-        <v>50</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="21">
-        <v>100</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7">
-        <v>255</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="21">
-        <v>20</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
     <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C2" s="6"/>
       <c r="D2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="26">
-        <v>50</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C3" s="26"/>
       <c r="D3" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="26">
-        <v>50</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C4" s="26"/>
       <c r="D4" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>132</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>133</v>
+      <c r="A5" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>5</v>
@@ -3180,15 +2651,15 @@
         <v>50</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>5</v>
@@ -3197,52 +2668,46 @@
         <v>20</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>26</v>
+        <v>292</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="9"/>
       <c r="E11" s="21" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>141</v>
-      </c>
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3250,7 +2715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3261,113 +2726,107 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="28" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="12">
-        <v>50</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>131</v>
+      <c r="E3" s="29" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>8</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="22"/>
       <c r="D4" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>41</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="22"/>
       <c r="D5" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>5</v>
@@ -3376,38 +2835,38 @@
         <v>50</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3415,7 +2874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3431,74 +2890,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C2" s="6"/>
       <c r="D2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="26">
-        <v>50</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C3" s="26"/>
       <c r="D3" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>5</v>
@@ -3507,15 +2962,15 @@
         <v>100</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>5</v>
@@ -3524,15 +2979,15 @@
         <v>100</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>5</v>
@@ -3541,53 +2996,53 @@
         <v>50</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3612,25 +3067,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>4</v>
@@ -3639,30 +3094,32 @@
         <v>7</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="C3" s="12">
+        <v>10</v>
+      </c>
       <c r="D3" s="13" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>5</v>
@@ -3671,15 +3128,15 @@
         <v>200</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>175</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>5</v>
@@ -3688,15 +3145,15 @@
         <v>200</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>47</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>5</v>
@@ -3705,10 +3162,10 @@
         <v>100</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -3731,7 +3188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3747,42 +3204,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>5</v>
@@ -3791,23 +3248,23 @@
         <v>100</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="21" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3831,40 +3288,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -3873,15 +3330,15 @@
         <v>10</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>5</v>
@@ -3890,10 +3347,10 @@
         <v>500</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
@@ -3906,4 +3363,1873 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="9">
+        <v>70</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="21">
+        <v>10</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="21">
+        <v>100</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="21">
+        <v>100</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="24">
+        <v>10</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="21">
+        <v>210</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="21">
+        <v>20</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9">
+        <v>50</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="21">
+        <v>50</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="21">
+        <v>100</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="41" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45"/>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="16">
+        <v>50</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="17">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="18">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="18">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="17">
+        <v>100</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="20">
+        <v>50</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="8">
+        <v>50</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9">
+        <v>100</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="42"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="5" max="5" width="39.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="8">
+        <v>50</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9">
+        <v>100</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="29">
+        <v>10</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="20">
+        <v>20</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="20">
+        <v>20</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="61.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="20">
+        <v>20</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="5" max="5" width="66.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="20">
+        <v>20</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="50.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="20">
+        <v>20</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="49.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="50">
+        <v>20</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="12">
+        <v>20</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="12">
+        <v>50</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="21">
+        <v>100</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>100</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="21">
+        <v>20</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>